--- a/Datasheet&Sch/Calc.xlsx
+++ b/Datasheet&Sch/Calc.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ilker\Documents\Arduino\Fragrance\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ilker\Documents\Arduino\Fragrance\Datasheet&amp;Sch\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A0FBAF0E-8B84-4020-8113-EAAB155B0AA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A45AA3A6-2515-4218-AB53-8662B5F165F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Adc" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="33">
   <si>
     <t xml:space="preserve">High Pulse </t>
   </si>
@@ -96,6 +97,45 @@
   </si>
   <si>
     <t>Minimum</t>
+  </si>
+  <si>
+    <t>adc</t>
+  </si>
+  <si>
+    <t>mVolt</t>
+  </si>
+  <si>
+    <t>up Res Kohm</t>
+  </si>
+  <si>
+    <t>Down Res Kohm</t>
+  </si>
+  <si>
+    <t>Mvolt</t>
+  </si>
+  <si>
+    <t>Sampled</t>
+  </si>
+  <si>
+    <t>Max mVolt</t>
+  </si>
+  <si>
+    <t>Adc Res</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adc </t>
+  </si>
+  <si>
+    <t>ESP32 Read</t>
+  </si>
+  <si>
+    <t>1327 mv</t>
+  </si>
+  <si>
+    <t>1000 adc</t>
+  </si>
+  <si>
+    <t>ss</t>
   </si>
 </sst>
 </file>
@@ -858,4 +898,822 @@
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BEDCC46-0EDA-47F4-8968-3F5EC7C8C76C}">
+  <dimension ref="A1:T24"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="3" max="3" width="11" customWidth="1"/>
+    <col min="4" max="4" width="13.6640625" customWidth="1"/>
+    <col min="6" max="6" width="11.109375" customWidth="1"/>
+    <col min="8" max="13" width="8.88671875" style="2"/>
+    <col min="15" max="15" width="10" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:20">
+      <c r="B1" s="2"/>
+      <c r="E1" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20">
+      <c r="B2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F2" t="s">
+        <v>26</v>
+      </c>
+      <c r="G2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20">
+      <c r="B3" s="2">
+        <v>5000</v>
+      </c>
+      <c r="C3">
+        <v>680</v>
+      </c>
+      <c r="D3">
+        <v>300</v>
+      </c>
+      <c r="E3" s="2">
+        <f>B3/(C3+D3)*D3</f>
+        <v>1530.612244897959</v>
+      </c>
+      <c r="F3">
+        <v>3300</v>
+      </c>
+      <c r="G3">
+        <v>4096</v>
+      </c>
+      <c r="H3" s="2">
+        <f>(E3*F3)/G3</f>
+        <v>1233.1592793367345</v>
+      </c>
+      <c r="I3" s="2">
+        <f>H3*F3/G3</f>
+        <v>993.51211470000578</v>
+      </c>
+      <c r="J3" s="2">
+        <f>I3*(D3/(D3+C3))</f>
+        <v>304.1363616428589</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20">
+      <c r="B4" s="2">
+        <v>4750</v>
+      </c>
+      <c r="C4">
+        <v>680</v>
+      </c>
+      <c r="D4">
+        <v>300</v>
+      </c>
+      <c r="E4" s="2">
+        <f t="shared" ref="E4:E19" si="0">B4/(C4+D4)*D4</f>
+        <v>1454.0816326530612</v>
+      </c>
+      <c r="F4">
+        <v>3300</v>
+      </c>
+      <c r="G4">
+        <v>4096</v>
+      </c>
+      <c r="H4" s="2">
+        <f t="shared" ref="H4:H24" si="1">(E4*F4)/G4</f>
+        <v>1171.5013153698978</v>
+      </c>
+      <c r="I4" s="2">
+        <f t="shared" ref="I4:I24" si="2">H4*F4/G4</f>
+        <v>943.83650896500558</v>
+      </c>
+      <c r="J4" s="2">
+        <f t="shared" ref="J4:J24" si="3">I4*(D4/(D4+C4))</f>
+        <v>288.92954356071601</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20">
+      <c r="B5" s="2">
+        <v>4500</v>
+      </c>
+      <c r="C5">
+        <v>680</v>
+      </c>
+      <c r="D5">
+        <v>300</v>
+      </c>
+      <c r="E5" s="2">
+        <f t="shared" si="0"/>
+        <v>1377.5510204081634</v>
+      </c>
+      <c r="F5">
+        <v>3300</v>
+      </c>
+      <c r="G5">
+        <v>4096</v>
+      </c>
+      <c r="H5" s="2">
+        <f t="shared" si="1"/>
+        <v>1109.8433514030612</v>
+      </c>
+      <c r="I5" s="2">
+        <f t="shared" si="2"/>
+        <v>894.16090323000537</v>
+      </c>
+      <c r="J5" s="2">
+        <f t="shared" si="3"/>
+        <v>273.72272547857307</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20">
+      <c r="A6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" s="2">
+        <v>4333</v>
+      </c>
+      <c r="C6">
+        <v>680</v>
+      </c>
+      <c r="D6">
+        <v>300</v>
+      </c>
+      <c r="E6" s="2">
+        <f t="shared" si="0"/>
+        <v>1326.4285714285716</v>
+      </c>
+      <c r="F6">
+        <v>3300</v>
+      </c>
+      <c r="G6">
+        <v>4096</v>
+      </c>
+      <c r="H6" s="2">
+        <f t="shared" si="1"/>
+        <v>1068.6558314732144</v>
+      </c>
+      <c r="I6" s="2">
+        <f t="shared" si="2"/>
+        <v>860.97759859902533</v>
+      </c>
+      <c r="J6" s="2">
+        <f t="shared" si="3"/>
+        <v>263.56457099970163</v>
+      </c>
+      <c r="M6" s="2">
+        <f>E6*(C6+D6)/D6</f>
+        <v>4333.0000000000009</v>
+      </c>
+      <c r="N6">
+        <f>(C6+D6)/D6</f>
+        <v>3.2666666666666666</v>
+      </c>
+      <c r="O6">
+        <f>E6*N6</f>
+        <v>4333</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20">
+      <c r="B7" s="2">
+        <v>4250</v>
+      </c>
+      <c r="C7">
+        <v>680</v>
+      </c>
+      <c r="D7">
+        <v>300</v>
+      </c>
+      <c r="E7" s="2">
+        <f t="shared" ref="E7" si="4">B7/(C7+D7)*D7</f>
+        <v>1301.0204081632653</v>
+      </c>
+      <c r="F7">
+        <v>3300</v>
+      </c>
+      <c r="G7">
+        <v>4096</v>
+      </c>
+      <c r="H7" s="2">
+        <f t="shared" ref="H7" si="5">(E7*F7)/G7</f>
+        <v>1048.1853874362246</v>
+      </c>
+      <c r="I7" s="2">
+        <f t="shared" ref="I7" si="6">H7*F7/G7</f>
+        <v>844.48529749500517</v>
+      </c>
+      <c r="J7" s="2">
+        <f t="shared" ref="J7" si="7">I7*(D7/(D7+C7))</f>
+        <v>258.51590739643018</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20">
+      <c r="B8" s="2">
+        <v>4000</v>
+      </c>
+      <c r="C8">
+        <v>680</v>
+      </c>
+      <c r="D8">
+        <v>300</v>
+      </c>
+      <c r="E8" s="2">
+        <f t="shared" si="0"/>
+        <v>1224.4897959183675</v>
+      </c>
+      <c r="F8">
+        <v>3300</v>
+      </c>
+      <c r="G8">
+        <v>4096</v>
+      </c>
+      <c r="H8" s="2">
+        <f t="shared" si="1"/>
+        <v>986.52742346938783</v>
+      </c>
+      <c r="I8" s="2">
+        <f t="shared" si="2"/>
+        <v>794.80969176000485</v>
+      </c>
+      <c r="J8" s="2">
+        <f t="shared" si="3"/>
+        <v>243.30908931428721</v>
+      </c>
+      <c r="M8" s="2">
+        <f>E8/D8*(C8+D8)</f>
+        <v>4000</v>
+      </c>
+      <c r="R8">
+        <v>5</v>
+      </c>
+      <c r="S8">
+        <v>1024</v>
+      </c>
+      <c r="T8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20">
+      <c r="B9" s="2">
+        <v>3750</v>
+      </c>
+      <c r="C9">
+        <v>680</v>
+      </c>
+      <c r="D9">
+        <v>300</v>
+      </c>
+      <c r="E9" s="2">
+        <f t="shared" si="0"/>
+        <v>1147.9591836734694</v>
+      </c>
+      <c r="F9">
+        <v>3300</v>
+      </c>
+      <c r="G9">
+        <v>4096</v>
+      </c>
+      <c r="H9" s="2">
+        <f t="shared" si="1"/>
+        <v>924.86945950255108</v>
+      </c>
+      <c r="I9" s="2">
+        <f t="shared" si="2"/>
+        <v>745.13408602500454</v>
+      </c>
+      <c r="J9" s="2">
+        <f t="shared" si="3"/>
+        <v>228.10227123214426</v>
+      </c>
+      <c r="R9">
+        <v>1</v>
+      </c>
+      <c r="S9">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20">
+      <c r="B10" s="2">
+        <v>3500</v>
+      </c>
+      <c r="C10">
+        <v>680</v>
+      </c>
+      <c r="D10">
+        <v>300</v>
+      </c>
+      <c r="E10" s="2">
+        <f t="shared" si="0"/>
+        <v>1071.4285714285716</v>
+      </c>
+      <c r="F10">
+        <v>3300</v>
+      </c>
+      <c r="G10">
+        <v>4096</v>
+      </c>
+      <c r="H10" s="2">
+        <f t="shared" si="1"/>
+        <v>863.21149553571433</v>
+      </c>
+      <c r="I10" s="2">
+        <f t="shared" si="2"/>
+        <v>695.45848029000422</v>
+      </c>
+      <c r="J10" s="2">
+        <f t="shared" si="3"/>
+        <v>212.89545315000129</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20">
+      <c r="B11" s="2">
+        <v>3250</v>
+      </c>
+      <c r="C11">
+        <v>680</v>
+      </c>
+      <c r="D11">
+        <v>300</v>
+      </c>
+      <c r="E11" s="2">
+        <f t="shared" si="0"/>
+        <v>994.89795918367349</v>
+      </c>
+      <c r="F11">
+        <v>3300</v>
+      </c>
+      <c r="G11">
+        <v>4096</v>
+      </c>
+      <c r="H11" s="2">
+        <f t="shared" si="1"/>
+        <v>801.55353156887759</v>
+      </c>
+      <c r="I11" s="2">
+        <f t="shared" si="2"/>
+        <v>645.7828745550039</v>
+      </c>
+      <c r="J11" s="2">
+        <f t="shared" si="3"/>
+        <v>197.68863506785834</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20">
+      <c r="B12" s="2">
+        <v>3000</v>
+      </c>
+      <c r="C12">
+        <v>680</v>
+      </c>
+      <c r="D12">
+        <v>300</v>
+      </c>
+      <c r="E12" s="2">
+        <f t="shared" si="0"/>
+        <v>918.36734693877543</v>
+      </c>
+      <c r="F12">
+        <v>3300</v>
+      </c>
+      <c r="G12">
+        <v>4096</v>
+      </c>
+      <c r="H12" s="2">
+        <f t="shared" si="1"/>
+        <v>739.89556760204073</v>
+      </c>
+      <c r="I12" s="2">
+        <f t="shared" si="2"/>
+        <v>596.10726882000347</v>
+      </c>
+      <c r="J12" s="2">
+        <f t="shared" si="3"/>
+        <v>182.48181698571534</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20">
+      <c r="B13" s="2">
+        <v>2750</v>
+      </c>
+      <c r="C13">
+        <v>680</v>
+      </c>
+      <c r="D13">
+        <v>300</v>
+      </c>
+      <c r="E13" s="2">
+        <f t="shared" si="0"/>
+        <v>841.83673469387759</v>
+      </c>
+      <c r="F13">
+        <v>3300</v>
+      </c>
+      <c r="G13">
+        <v>4096</v>
+      </c>
+      <c r="H13" s="2">
+        <f t="shared" si="1"/>
+        <v>678.2376036352041</v>
+      </c>
+      <c r="I13" s="2">
+        <f t="shared" si="2"/>
+        <v>546.43166308500327</v>
+      </c>
+      <c r="J13" s="2">
+        <f t="shared" si="3"/>
+        <v>167.27499890357242</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20">
+      <c r="B14" s="2">
+        <v>2500</v>
+      </c>
+      <c r="C14">
+        <v>680</v>
+      </c>
+      <c r="D14">
+        <v>300</v>
+      </c>
+      <c r="E14" s="2">
+        <f t="shared" si="0"/>
+        <v>765.30612244897952</v>
+      </c>
+      <c r="F14">
+        <v>3300</v>
+      </c>
+      <c r="G14">
+        <v>4096</v>
+      </c>
+      <c r="H14" s="2">
+        <f t="shared" si="1"/>
+        <v>616.57963966836724</v>
+      </c>
+      <c r="I14" s="2">
+        <f t="shared" si="2"/>
+        <v>496.75605735000289</v>
+      </c>
+      <c r="J14" s="2">
+        <f t="shared" si="3"/>
+        <v>152.06818082142945</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20">
+      <c r="B15" s="2">
+        <v>2250</v>
+      </c>
+      <c r="C15">
+        <v>680</v>
+      </c>
+      <c r="D15">
+        <v>300</v>
+      </c>
+      <c r="E15" s="2">
+        <f t="shared" si="0"/>
+        <v>688.77551020408168</v>
+      </c>
+      <c r="F15">
+        <v>3300</v>
+      </c>
+      <c r="G15">
+        <v>4096</v>
+      </c>
+      <c r="H15" s="2">
+        <f t="shared" si="1"/>
+        <v>554.9216757015306</v>
+      </c>
+      <c r="I15" s="2">
+        <f t="shared" si="2"/>
+        <v>447.08045161500269</v>
+      </c>
+      <c r="J15" s="2">
+        <f t="shared" si="3"/>
+        <v>136.86136273928653</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20">
+      <c r="B16" s="2">
+        <v>2000</v>
+      </c>
+      <c r="C16">
+        <v>680</v>
+      </c>
+      <c r="D16">
+        <v>300</v>
+      </c>
+      <c r="E16" s="2">
+        <f t="shared" si="0"/>
+        <v>612.24489795918373</v>
+      </c>
+      <c r="F16">
+        <v>3300</v>
+      </c>
+      <c r="G16">
+        <v>4096</v>
+      </c>
+      <c r="H16" s="2">
+        <f t="shared" si="1"/>
+        <v>493.26371173469391</v>
+      </c>
+      <c r="I16" s="2">
+        <f t="shared" si="2"/>
+        <v>397.40484588000243</v>
+      </c>
+      <c r="J16" s="2">
+        <f t="shared" si="3"/>
+        <v>121.6545446571436</v>
+      </c>
+    </row>
+    <row r="17" spans="2:17">
+      <c r="B17" s="2">
+        <v>1750</v>
+      </c>
+      <c r="C17">
+        <v>680</v>
+      </c>
+      <c r="D17">
+        <v>300</v>
+      </c>
+      <c r="E17" s="2">
+        <f t="shared" si="0"/>
+        <v>535.71428571428578</v>
+      </c>
+      <c r="F17">
+        <v>3300</v>
+      </c>
+      <c r="G17">
+        <v>4096</v>
+      </c>
+      <c r="H17" s="2">
+        <f t="shared" si="1"/>
+        <v>431.60574776785717</v>
+      </c>
+      <c r="I17" s="2">
+        <f t="shared" si="2"/>
+        <v>347.72924014500211</v>
+      </c>
+      <c r="J17" s="2">
+        <f t="shared" si="3"/>
+        <v>106.44772657500064</v>
+      </c>
+    </row>
+    <row r="18" spans="2:17">
+      <c r="B18" s="2">
+        <v>1500</v>
+      </c>
+      <c r="C18">
+        <v>680</v>
+      </c>
+      <c r="D18">
+        <v>300</v>
+      </c>
+      <c r="E18" s="2">
+        <f t="shared" si="0"/>
+        <v>459.18367346938771</v>
+      </c>
+      <c r="F18">
+        <v>3300</v>
+      </c>
+      <c r="G18">
+        <v>4096</v>
+      </c>
+      <c r="H18" s="2">
+        <f t="shared" si="1"/>
+        <v>369.94778380102036</v>
+      </c>
+      <c r="I18" s="2">
+        <f t="shared" si="2"/>
+        <v>298.05363441000173</v>
+      </c>
+      <c r="J18" s="2">
+        <f t="shared" si="3"/>
+        <v>91.24090849285767</v>
+      </c>
+    </row>
+    <row r="19" spans="2:17">
+      <c r="B19" s="2">
+        <v>1250</v>
+      </c>
+      <c r="C19">
+        <v>680</v>
+      </c>
+      <c r="D19">
+        <v>300</v>
+      </c>
+      <c r="E19" s="2">
+        <f t="shared" si="0"/>
+        <v>382.65306122448976</v>
+      </c>
+      <c r="F19">
+        <v>3300</v>
+      </c>
+      <c r="G19">
+        <v>4096</v>
+      </c>
+      <c r="H19" s="2">
+        <f t="shared" si="1"/>
+        <v>308.28981983418362</v>
+      </c>
+      <c r="I19" s="2">
+        <f t="shared" si="2"/>
+        <v>248.37802867500145</v>
+      </c>
+      <c r="J19" s="2">
+        <f t="shared" si="3"/>
+        <v>76.034090410714725</v>
+      </c>
+    </row>
+    <row r="20" spans="2:17">
+      <c r="B20" s="2">
+        <v>1000</v>
+      </c>
+      <c r="C20">
+        <v>680</v>
+      </c>
+      <c r="D20">
+        <v>300</v>
+      </c>
+      <c r="E20" s="2">
+        <f>B20/(C20+D20)*D20</f>
+        <v>306.12244897959187</v>
+      </c>
+      <c r="F20">
+        <v>3300</v>
+      </c>
+      <c r="G20">
+        <v>4096</v>
+      </c>
+      <c r="H20" s="2">
+        <f t="shared" si="1"/>
+        <v>246.63185586734696</v>
+      </c>
+      <c r="I20" s="2">
+        <f t="shared" si="2"/>
+        <v>198.70242294000121</v>
+      </c>
+      <c r="J20" s="2">
+        <f t="shared" si="3"/>
+        <v>60.827272328571802</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="21" spans="2:17">
+      <c r="B21" s="2">
+        <v>750</v>
+      </c>
+      <c r="C21">
+        <v>680</v>
+      </c>
+      <c r="D21">
+        <v>300</v>
+      </c>
+      <c r="E21" s="2">
+        <f t="shared" ref="E21:E24" si="8">B21/(C21+D21)*D21</f>
+        <v>229.59183673469386</v>
+      </c>
+      <c r="F21">
+        <v>3300</v>
+      </c>
+      <c r="G21">
+        <v>4096</v>
+      </c>
+      <c r="H21" s="2">
+        <f t="shared" si="1"/>
+        <v>184.97389190051018</v>
+      </c>
+      <c r="I21" s="2">
+        <f t="shared" si="2"/>
+        <v>149.02681720500087</v>
+      </c>
+      <c r="J21" s="2">
+        <f t="shared" si="3"/>
+        <v>45.620454246428835</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="22" spans="2:17">
+      <c r="B22" s="2">
+        <v>500</v>
+      </c>
+      <c r="C22">
+        <v>680</v>
+      </c>
+      <c r="D22">
+        <v>300</v>
+      </c>
+      <c r="E22" s="2">
+        <f t="shared" si="8"/>
+        <v>153.06122448979593</v>
+      </c>
+      <c r="F22">
+        <v>3300</v>
+      </c>
+      <c r="G22">
+        <v>4096</v>
+      </c>
+      <c r="H22" s="2">
+        <f t="shared" si="1"/>
+        <v>123.31592793367348</v>
+      </c>
+      <c r="I22" s="2">
+        <f t="shared" si="2"/>
+        <v>99.351211470000607</v>
+      </c>
+      <c r="J22" s="2">
+        <f t="shared" si="3"/>
+        <v>30.413636164285901</v>
+      </c>
+    </row>
+    <row r="23" spans="2:17">
+      <c r="B23" s="2">
+        <v>250</v>
+      </c>
+      <c r="C23">
+        <v>680</v>
+      </c>
+      <c r="D23">
+        <v>300</v>
+      </c>
+      <c r="E23" s="2">
+        <f t="shared" si="8"/>
+        <v>76.530612244897966</v>
+      </c>
+      <c r="F23">
+        <v>3300</v>
+      </c>
+      <c r="G23">
+        <v>4096</v>
+      </c>
+      <c r="H23" s="2">
+        <f t="shared" si="1"/>
+        <v>61.657963966836739</v>
+      </c>
+      <c r="I23" s="2">
+        <f t="shared" si="2"/>
+        <v>49.675605735000303</v>
+      </c>
+      <c r="J23" s="2">
+        <f t="shared" si="3"/>
+        <v>15.20681808214295</v>
+      </c>
+    </row>
+    <row r="24" spans="2:17">
+      <c r="B24" s="2">
+        <v>0</v>
+      </c>
+      <c r="C24">
+        <v>680</v>
+      </c>
+      <c r="D24">
+        <v>300</v>
+      </c>
+      <c r="E24" s="2">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="F24">
+        <v>3300</v>
+      </c>
+      <c r="G24">
+        <v>4096</v>
+      </c>
+      <c r="H24" s="2">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I24" s="2">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J24" s="2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Datasheet&Sch/Calc.xlsx
+++ b/Datasheet&Sch/Calc.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ilker\Documents\Arduino\Fragrance\Datasheet&amp;Sch\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A45AA3A6-2515-4218-AB53-8662B5F165F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FA75FC7-689A-4D35-9F4E-3F41481DEDBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Adc" sheetId="3" r:id="rId2"/>
+    <sheet name="Key" sheetId="4" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="42">
   <si>
     <t xml:space="preserve">High Pulse </t>
   </si>
@@ -136,13 +137,80 @@
   </si>
   <si>
     <t>ss</t>
+  </si>
+  <si>
+    <t>Default</t>
+  </si>
+  <si>
+    <t>Pressed</t>
+  </si>
+  <si>
+    <t>Release</t>
+  </si>
+  <si>
+    <r>
+      <t>Key</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF4E5B61"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFD35400"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>TimerPress</t>
+    </r>
+  </si>
+  <si>
+    <t>return</t>
+  </si>
+  <si>
+    <t>+</t>
+  </si>
+  <si>
+    <t>Press Stlll</t>
+  </si>
+  <si>
+    <r>
+      <t>Key</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF4E5B61"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFD35400"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>Double_timer</t>
+    </r>
+  </si>
+  <si>
+    <t>&gt; 400msec</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -160,6 +228,18 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF4E5B61"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FFD35400"/>
+      <name val="Consolas"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="2">
@@ -182,12 +262,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1716,4 +1799,82 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E633C52C-477B-4CCA-83B5-D00BFF18F7AF}">
+  <dimension ref="A5:I12"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="4" max="4" width="15.5546875" customWidth="1"/>
+    <col min="5" max="5" width="15.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="5" spans="1:9">
+      <c r="D5" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6">
+        <v>1</v>
+      </c>
+      <c r="B6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="I6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8">
+        <v>2</v>
+      </c>
+      <c r="B8" t="s">
+        <v>34</v>
+      </c>
+      <c r="D8" t="s">
+        <v>38</v>
+      </c>
+      <c r="E8" t="s">
+        <v>38</v>
+      </c>
+      <c r="I8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10">
+        <v>3</v>
+      </c>
+      <c r="B10" t="s">
+        <v>39</v>
+      </c>
+      <c r="D10" t="s">
+        <v>38</v>
+      </c>
+      <c r="E10" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12">
+        <v>4</v>
+      </c>
+      <c r="B12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E12" t="s">
+        <v>41</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>